--- a/school_surveys/026_school_year_itinerary_survey--school_surveys.xlsx
+++ b/school_surveys/026_school_year_itinerary_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -821,7 +821,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Contact Email</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Emergency Contact Address</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1173,8 +1173,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'first_year'}</t>
+          <t>first_year</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'First Year'}</t>
+          <t>First Year</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'second_year'}</t>
+          <t>second_year</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Second Year'}</t>
+          <t>Second Year</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'third_year'}</t>
+          <t>third_year</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Third Year'}</t>
+          <t>Third Year</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'sibling'}</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Sibling'}</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'accomplishment_1'}</t>
+          <t>accomplishment_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Accomplishment 1'}</t>
+          <t>Accomplishment 1</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'accomplishment_2'}</t>
+          <t>accomplishment_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Accomplishment 2'}</t>
+          <t>Accomplishment 2</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'accomplishment_3'}</t>
+          <t>accomplishment_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Accomplishment 3'}</t>
+          <t>Accomplishment 3</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'art'}</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Art'}</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'music'}</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Music'}</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'dance'}</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Dance'}</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'art'}</t>
+          <t>art</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Art'}</t>
+          <t>Art</t>
         </is>
       </c>
     </row>
